--- a/data/trans_orig/Q17H_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q17H_R-Estudios-trans_orig.xlsx
@@ -677,12 +677,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,03</t>
+          <t>0,85; 1,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 0,95</t>
+          <t>0,72; 0,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -692,12 +692,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 0,68</t>
+          <t>0,52; 0,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,72</t>
+          <t>0,42; 0,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 0,82</t>
+          <t>0,69; 0,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 0,75</t>
+          <t>0,57; 0,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -787,12 +787,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 1,39</t>
+          <t>1,17; 1,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 1,1</t>
+          <t>0,92; 1,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 0,88</t>
+          <t>0,74; 0,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 0,71</t>
+          <t>0,59; 0,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,13</t>
+          <t>0,99; 1,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 0,9</t>
+          <t>0,79; 0,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -897,12 +897,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,26</t>
+          <t>0,97; 1,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,37</t>
+          <t>0,9; 1,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 0,92</t>
+          <t>0,67; 0,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 0,8</t>
+          <t>0,56; 0,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -927,12 +927,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,05</t>
+          <t>0,86; 1,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,03</t>
+          <t>0,76; 1,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,23</t>
+          <t>1,08; 1,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 0,84</t>
+          <t>0,74; 0,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
